--- a/results/tables/表2_各区域最优配置方案.xlsx
+++ b/results/tables/表2_各区域最优配置方案.xlsx
@@ -584,22 +584,22 @@
         <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K4" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -662,22 +662,22 @@
         <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>4.800000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9098000000000001</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K6" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -701,22 +701,22 @@
         <v>63</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>12.8</v>
+        <v>4.800000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9466</v>
+        <v>0.9964</v>
       </c>
       <c r="J7" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K7" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
@@ -740,22 +740,22 @@
         <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>5.600000000000001</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
         <v>0.9457</v>
       </c>
       <c r="J8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K8" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -818,22 +818,22 @@
         <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>12.4</v>
+        <v>5.600000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K10" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -857,22 +857,22 @@
         <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>6.8</v>
+        <v>5.600000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K11" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/results/tables/表2_各区域最优配置方案.xlsx
+++ b/results/tables/表2_各区域最优配置方案.xlsx
@@ -587,19 +587,19 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>11.2</v>
+        <v>0.8</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.9123</v>
       </c>
       <c r="J4" t="n">
         <v>129</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
@@ -662,22 +662,22 @@
         <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>12.4</v>
+        <v>18</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K6" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7">
@@ -701,22 +701,22 @@
         <v>63</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>4.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9964</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K7" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
@@ -740,22 +740,22 @@
         <v>30</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.9457</v>
-      </c>
       <c r="J8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K8" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9">
@@ -779,22 +779,22 @@
         <v>39</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H9" t="n">
-        <v>4.800000000000001</v>
+        <v>80</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9353</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K9" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
@@ -818,22 +818,22 @@
         <v>26</v>
       </c>
       <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="n">
-        <v>7</v>
-      </c>
       <c r="H10" t="n">
-        <v>5.600000000000001</v>
+        <v>24</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K10" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -857,22 +857,22 @@
         <v>35</v>
       </c>
       <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" t="n">
-        <v>7</v>
-      </c>
       <c r="H11" t="n">
-        <v>5.600000000000001</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K11" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/results/tables/表2_各区域最优配置方案.xlsx
+++ b/results/tables/表2_各区域最优配置方案.xlsx
@@ -509,19 +509,19 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9203</v>
+        <v>0.8076</v>
       </c>
       <c r="J2" t="n">
         <v>129</v>
       </c>
       <c r="K2" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
@@ -548,19 +548,19 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9411</v>
+        <v>0.7789</v>
       </c>
       <c r="J3" t="n">
         <v>129</v>
       </c>
       <c r="K3" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4">
@@ -587,19 +587,19 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9123</v>
+        <v>0.8229</v>
       </c>
       <c r="J4" t="n">
         <v>129</v>
       </c>
       <c r="K4" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
@@ -608,7 +608,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -623,22 +623,22 @@
         <v>73</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9193</v>
+        <v>0.7516</v>
       </c>
       <c r="J5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K5" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6">
@@ -647,7 +647,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -662,22 +662,22 @@
         <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H6" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9098000000000001</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K6" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
@@ -701,19 +701,19 @@
         <v>63</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.9466</v>
       </c>
       <c r="J7" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K7" t="n">
         <v>91</v>
@@ -725,7 +725,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -740,22 +740,22 @@
         <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>6.4</v>
+        <v>32.4</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="K8" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -764,7 +764,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -779,22 +779,22 @@
         <v>39</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>80</v>
+        <v>60.8</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="K9" t="n">
-        <v>111</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10">
@@ -803,7 +803,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -818,22 +818,22 @@
         <v>26</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
         <v>4</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>24</v>
-      </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0.7724</v>
       </c>
       <c r="J10" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K10" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
@@ -842,7 +842,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -857,22 +857,22 @@
         <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H11" t="n">
-        <v>12</v>
+        <v>69.2</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K11" t="n">
-        <v>86</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
